--- a/Store Support/Projects/JobCodes-teaming/Teaming/TMS Data (3).xlsx
+++ b/Store Support/Projects/JobCodes-teaming/Teaming/TMS Data (3).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://my.wal-mart.com/personal/krush_homeoffice_wal-mart_com/Documents/Documents/VSCode/Activity_Hub/Store Support/Projects/JobCodes-teaming/Teaming/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6BA335-3A26-4F85-B77D-2CDBAF97D659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{681EDC71-CAE6-415D-AB1E-0A090213AE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="4155" windowWidth="15585" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
